--- a/pay3.xlsx
+++ b/pay3.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="187">
   <si>
     <t>#</t>
   </si>
@@ -95,6 +95,135 @@
     <t>اديان عماد حميد حسن</t>
   </si>
   <si>
+    <t>امنه عمر سعدون جاسم</t>
+  </si>
+  <si>
+    <t>1,575,000</t>
+  </si>
+  <si>
+    <t>امير علي حسن حاتم</t>
+  </si>
+  <si>
+    <t>امير ناصر جاني كاظم</t>
+  </si>
+  <si>
+    <t>ايناس باسم اسماعيل لطيف</t>
+  </si>
+  <si>
+    <t>ايناس هاشم كريم عباس</t>
+  </si>
+  <si>
+    <t>ايه فوزي مشكور مردان</t>
+  </si>
+  <si>
+    <t>ايه قاسم سعيد ناصر</t>
+  </si>
+  <si>
+    <t>أمير انور علاوي حسين</t>
+  </si>
+  <si>
+    <t>براء ابراهيم محمود محمد</t>
+  </si>
+  <si>
+    <t>بشير حسين علي حسين</t>
+  </si>
+  <si>
+    <t>تبارك هادي كاظم سفيح</t>
+  </si>
+  <si>
+    <t>حسن حيدر محمد مهدي</t>
+  </si>
+  <si>
+    <t>حسين عباس محمود عبد</t>
+  </si>
+  <si>
+    <t>2,100,000</t>
+  </si>
+  <si>
+    <t>150,000</t>
+  </si>
+  <si>
+    <t>93.33%</t>
+  </si>
+  <si>
+    <t>حسين عبد الكريم جواد صفر</t>
+  </si>
+  <si>
+    <t>حسين علي كمال مرهون</t>
+  </si>
+  <si>
+    <t>1,800,000</t>
+  </si>
+  <si>
+    <t>2,025,000</t>
+  </si>
+  <si>
+    <t>حسين محمد فالح حسن</t>
+  </si>
+  <si>
+    <t>حوراء حيدر عبد الرزاق ناجي</t>
+  </si>
+  <si>
+    <t>خالد محمد حسين عباس</t>
+  </si>
+  <si>
+    <t>رقيه محسن جبير ناصر</t>
+  </si>
+  <si>
+    <t>رؤى ثامر عاشور خدي</t>
+  </si>
+  <si>
+    <t>رؤى جعفر كامل عباس</t>
+  </si>
+  <si>
+    <t>زهراء حسام ناصر محمد</t>
+  </si>
+  <si>
+    <t>زهراء محمد حسين علوان</t>
+  </si>
+  <si>
+    <t>زينب معد فالح حسن</t>
+  </si>
+  <si>
+    <t>سجاد ماجد حسين علوان</t>
+  </si>
+  <si>
+    <t>شهد نوري سعدون شمران</t>
+  </si>
+  <si>
+    <t>شيفان خليل محمد ملك</t>
+  </si>
+  <si>
+    <t>طه رعد جبير جميس</t>
+  </si>
+  <si>
+    <t>0%</t>
+  </si>
+  <si>
+    <t>أقل من 25%</t>
+  </si>
+  <si>
+    <t>طيبه عدنان عبد الجبار عبد الكريم</t>
+  </si>
+  <si>
+    <t>عباس خليل حيدر ادهم</t>
+  </si>
+  <si>
+    <t>1,500,000</t>
+  </si>
+  <si>
+    <t>750,000</t>
+  </si>
+  <si>
+    <t>66.67%</t>
+  </si>
+  <si>
+    <t>مسدد 50%+</t>
+  </si>
+  <si>
+    <t>عباس علي حسين داخل</t>
+  </si>
+  <si>
     <t>1,250,000</t>
   </si>
   <si>
@@ -104,135 +233,6 @@
     <t>55.56%</t>
   </si>
   <si>
-    <t>مسدد 50%+</t>
-  </si>
-  <si>
-    <t>امنه عمر سعدون جاسم</t>
-  </si>
-  <si>
-    <t>1,575,000</t>
-  </si>
-  <si>
-    <t>امير علي حسن حاتم</t>
-  </si>
-  <si>
-    <t>امير ناصر جاني كاظم</t>
-  </si>
-  <si>
-    <t>ايناس باسم اسماعيل لطيف</t>
-  </si>
-  <si>
-    <t>ايناس هاشم كريم عباس</t>
-  </si>
-  <si>
-    <t>ايه فوزي مشكور مردان</t>
-  </si>
-  <si>
-    <t>ايه قاسم سعيد ناصر</t>
-  </si>
-  <si>
-    <t>أمير انور علاوي حسين</t>
-  </si>
-  <si>
-    <t>براء ابراهيم محمود محمد</t>
-  </si>
-  <si>
-    <t>بشير حسين علي حسين</t>
-  </si>
-  <si>
-    <t>تبارك هادي كاظم سفيح</t>
-  </si>
-  <si>
-    <t>حسن حيدر محمد مهدي</t>
-  </si>
-  <si>
-    <t>حسين عباس محمود عبد</t>
-  </si>
-  <si>
-    <t>2,100,000</t>
-  </si>
-  <si>
-    <t>150,000</t>
-  </si>
-  <si>
-    <t>93.33%</t>
-  </si>
-  <si>
-    <t>حسين عبد الكريم جواد صفر</t>
-  </si>
-  <si>
-    <t>حسين علي كمال مرهون</t>
-  </si>
-  <si>
-    <t>1,800,000</t>
-  </si>
-  <si>
-    <t>2,025,000</t>
-  </si>
-  <si>
-    <t>حسين محمد فالح حسن</t>
-  </si>
-  <si>
-    <t>حوراء حيدر عبد الرزاق ناجي</t>
-  </si>
-  <si>
-    <t>خالد محمد حسين عباس</t>
-  </si>
-  <si>
-    <t>رقيه محسن جبير ناصر</t>
-  </si>
-  <si>
-    <t>رؤى ثامر عاشور خدي</t>
-  </si>
-  <si>
-    <t>رؤى جعفر كامل عباس</t>
-  </si>
-  <si>
-    <t>زهراء حسام ناصر محمد</t>
-  </si>
-  <si>
-    <t>زهراء محمد حسين علوان</t>
-  </si>
-  <si>
-    <t>زينب معد فالح حسن</t>
-  </si>
-  <si>
-    <t>سجاد ماجد حسين علوان</t>
-  </si>
-  <si>
-    <t>شهد نوري سعدون شمران</t>
-  </si>
-  <si>
-    <t>شيفان خليل محمد ملك</t>
-  </si>
-  <si>
-    <t>طه رعد جبير جميس</t>
-  </si>
-  <si>
-    <t>0%</t>
-  </si>
-  <si>
-    <t>أقل من 25%</t>
-  </si>
-  <si>
-    <t>طيبه عدنان عبد الجبار عبد الكريم</t>
-  </si>
-  <si>
-    <t>عباس خليل حيدر ادهم</t>
-  </si>
-  <si>
-    <t>1,500,000</t>
-  </si>
-  <si>
-    <t>750,000</t>
-  </si>
-  <si>
-    <t>66.67%</t>
-  </si>
-  <si>
-    <t>عباس علي حسين داخل</t>
-  </si>
-  <si>
     <t>عبد الرحمن رائد عبد الحميد محمود</t>
   </si>
   <si>
@@ -399,15 +399,6 @@
   </si>
   <si>
     <t>مهدي احمد عبد الأمير عبد الحسين</t>
-  </si>
-  <si>
-    <t>1,120,000</t>
-  </si>
-  <si>
-    <t>1,130,000</t>
-  </si>
-  <si>
-    <t>49.78%</t>
   </si>
   <si>
     <t>مهدي علي نبيل صالح</t>
@@ -645,13 +636,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFE699"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFFFE699"/>
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
@@ -1133,32 +1124,32 @@
       </c>
     </row>
     <row r="5" spans="1:9">
-      <c r="A5" s="5">
+      <c r="A5" s="4">
         <v>4</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C5" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="I5" s="5" t="s">
-        <v>29</v>
+      <c r="C5" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" s="4">
+        <v>0</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -1166,7 +1157,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>10</v>
@@ -1175,10 +1166,10 @@
         <v>11</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="G6" s="4">
         <v>0</v>
@@ -1195,7 +1186,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>10</v>
@@ -1224,7 +1215,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>10</v>
@@ -1253,7 +1244,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>10</v>
@@ -1282,7 +1273,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>10</v>
@@ -1311,7 +1302,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>10</v>
@@ -1340,7 +1331,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>10</v>
@@ -1369,7 +1360,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>10</v>
@@ -1398,7 +1389,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>10</v>
@@ -1427,7 +1418,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>10</v>
@@ -1456,7 +1447,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>10</v>
@@ -1485,7 +1476,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>10</v>
@@ -1514,7 +1505,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>10</v>
@@ -1526,13 +1517,13 @@
         <v>12</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>16</v>
@@ -1543,7 +1534,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>10</v>
@@ -1572,7 +1563,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>10</v>
@@ -1581,10 +1572,10 @@
         <v>11</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G20" s="4">
         <v>0</v>
@@ -1601,7 +1592,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="C21" s="4" t="s">
         <v>10</v>
@@ -1630,7 +1621,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>10</v>
@@ -1639,10 +1630,10 @@
         <v>11</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G22" s="4">
         <v>0</v>
@@ -1659,7 +1650,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>10</v>
@@ -1688,7 +1679,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C24" s="4" t="s">
         <v>10</v>
@@ -1717,7 +1708,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>10</v>
@@ -1726,10 +1717,10 @@
         <v>11</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G25" s="4">
         <v>0</v>
@@ -1746,7 +1737,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C26" s="4" t="s">
         <v>10</v>
@@ -1775,7 +1766,7 @@
         <v>26</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C27" s="4" t="s">
         <v>10</v>
@@ -1784,10 +1775,10 @@
         <v>11</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G27" s="4">
         <v>0</v>
@@ -1804,7 +1795,7 @@
         <v>27</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>10</v>
@@ -1813,10 +1804,10 @@
         <v>11</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G28" s="4">
         <v>0</v>
@@ -1833,7 +1824,7 @@
         <v>28</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>10</v>
@@ -1842,10 +1833,10 @@
         <v>11</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G29" s="4">
         <v>0</v>
@@ -1862,7 +1853,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C30" s="4" t="s">
         <v>10</v>
@@ -1891,7 +1882,7 @@
         <v>30</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C31" s="4" t="s">
         <v>10</v>
@@ -1920,7 +1911,7 @@
         <v>31</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C32" s="4" t="s">
         <v>10</v>
@@ -1929,10 +1920,10 @@
         <v>11</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G32" s="4">
         <v>0</v>
@@ -1945,32 +1936,32 @@
       </c>
     </row>
     <row r="33" spans="1:9">
-      <c r="A33" s="6">
+      <c r="A33" s="5">
         <v>32</v>
       </c>
-      <c r="B33" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="C33" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D33" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E33" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="F33" s="6">
-        <v>0</v>
-      </c>
-      <c r="G33" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="H33" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I33" s="6" t="s">
-        <v>65</v>
+      <c r="B33" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E33" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F33" s="5">
+        <v>0</v>
+      </c>
+      <c r="G33" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="H33" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="I33" s="5" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="34" spans="1:9">
@@ -1978,144 +1969,144 @@
         <v>33</v>
       </c>
       <c r="B34" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G34" s="4">
+        <v>0</v>
+      </c>
+      <c r="H34" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I34" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9">
+      <c r="A35" s="6">
+        <v>34</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F35" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="G35" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="H35" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="C34" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D34" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E34" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F34" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G34" s="4">
-        <v>0</v>
-      </c>
-      <c r="H34" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="I34" s="4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9">
-      <c r="A35" s="5">
-        <v>34</v>
-      </c>
-      <c r="B35" s="5" t="s">
+      <c r="I35" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="C35" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D35" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E35" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F35" s="5" t="s">
+    </row>
+    <row r="36" spans="1:9">
+      <c r="A36" s="6">
+        <v>35</v>
+      </c>
+      <c r="B36" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="G35" s="5" t="s">
+      <c r="C36" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F36" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="H35" s="5" t="s">
+      <c r="G36" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="I35" s="5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9">
-      <c r="A36" s="5">
-        <v>35</v>
-      </c>
-      <c r="B36" s="5" t="s">
+      <c r="H36" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="C36" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D36" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E36" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F36" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="G36" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="H36" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="I36" s="5" t="s">
-        <v>29</v>
+      <c r="I36" s="6" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="37" spans="1:9">
-      <c r="A37" s="6">
+      <c r="A37" s="5">
         <v>36</v>
       </c>
-      <c r="B37" s="6" t="s">
+      <c r="B37" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="C37" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D37" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E37" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F37" s="6">
-        <v>0</v>
-      </c>
-      <c r="G37" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="H37" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I37" s="6" t="s">
-        <v>65</v>
+      <c r="C37" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E37" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F37" s="5">
+        <v>0</v>
+      </c>
+      <c r="G37" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H37" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="I37" s="5" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="38" spans="1:9">
-      <c r="A38" s="5">
+      <c r="A38" s="6">
         <v>37</v>
       </c>
-      <c r="B38" s="5" t="s">
+      <c r="B38" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="C38" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D38" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E38" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F38" s="5" t="s">
+      <c r="C38" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E38" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F38" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="G38" s="5" t="s">
+      <c r="G38" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="H38" s="5" t="s">
+      <c r="H38" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="I38" s="5" t="s">
-        <v>29</v>
+      <c r="I38" s="6" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="39" spans="1:9">
@@ -2222,10 +2213,10 @@
         <v>12</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>27</v>
+        <v>70</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>26</v>
+        <v>69</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>20</v>
@@ -2248,10 +2239,10 @@
         <v>11</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G43" s="4">
         <v>0</v>
@@ -2264,61 +2255,61 @@
       </c>
     </row>
     <row r="44" spans="1:9">
-      <c r="A44" s="5">
+      <c r="A44" s="6">
         <v>43</v>
       </c>
-      <c r="B44" s="5" t="s">
+      <c r="B44" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="C44" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D44" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E44" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F44" s="5" t="s">
+      <c r="C44" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D44" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E44" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F44" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="G44" s="5" t="s">
+      <c r="G44" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="H44" s="5" t="s">
+      <c r="H44" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="I44" s="5" t="s">
-        <v>29</v>
+      <c r="I44" s="6" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="45" spans="1:9">
-      <c r="A45" s="6">
+      <c r="A45" s="5">
         <v>44</v>
       </c>
-      <c r="B45" s="6" t="s">
+      <c r="B45" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="C45" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D45" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E45" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F45" s="6">
-        <v>0</v>
-      </c>
-      <c r="G45" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="H45" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I45" s="6" t="s">
-        <v>65</v>
+      <c r="C45" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D45" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E45" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F45" s="5">
+        <v>0</v>
+      </c>
+      <c r="G45" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H45" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="I45" s="5" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="46" spans="1:9">
@@ -2480,10 +2471,10 @@
         <v>11</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>96</v>
@@ -2496,32 +2487,32 @@
       </c>
     </row>
     <row r="52" spans="1:9">
-      <c r="A52" s="6">
+      <c r="A52" s="5">
         <v>51</v>
       </c>
-      <c r="B52" s="6" t="s">
+      <c r="B52" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="C52" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D52" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E52" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F52" s="6" t="s">
+      <c r="C52" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D52" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E52" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F52" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="G52" s="6" t="s">
+      <c r="G52" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="H52" s="6" t="s">
+      <c r="H52" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="I52" s="6" t="s">
-        <v>65</v>
+      <c r="I52" s="5" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="53" spans="1:9">
@@ -2554,61 +2545,61 @@
       </c>
     </row>
     <row r="54" spans="1:9">
-      <c r="A54" s="5">
+      <c r="A54" s="6">
         <v>53</v>
       </c>
-      <c r="B54" s="5" t="s">
+      <c r="B54" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="C54" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D54" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E54" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F54" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="G54" s="5" t="s">
+      <c r="C54" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D54" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E54" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F54" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="G54" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="H54" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="I54" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9">
+      <c r="A55" s="5">
+        <v>54</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="C55" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D55" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E55" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F55" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="G55" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="H54" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="I54" s="5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9">
-      <c r="A55" s="6">
-        <v>54</v>
-      </c>
-      <c r="B55" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="C55" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D55" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E55" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="F55" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="G55" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="H55" s="6" t="s">
+      <c r="H55" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="I55" s="6" t="s">
-        <v>65</v>
+      <c r="I55" s="5" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="56" spans="1:9">
@@ -2657,10 +2648,10 @@
         <v>12</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>27</v>
+        <v>70</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>26</v>
+        <v>69</v>
       </c>
       <c r="H57" s="3" t="s">
         <v>20</v>
@@ -2670,32 +2661,32 @@
       </c>
     </row>
     <row r="58" spans="1:9">
-      <c r="A58" s="5">
+      <c r="A58" s="6">
         <v>57</v>
       </c>
-      <c r="B58" s="5" t="s">
+      <c r="B58" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="C58" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D58" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E58" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F58" s="5" t="s">
+      <c r="C58" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D58" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E58" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F58" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="G58" s="5" t="s">
+      <c r="G58" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="H58" s="5" t="s">
+      <c r="H58" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="I58" s="5" t="s">
-        <v>29</v>
+      <c r="I58" s="6" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="59" spans="1:9">
@@ -2712,10 +2703,10 @@
         <v>11</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G59" s="4">
         <v>0</v>
@@ -2831,7 +2822,7 @@
         <v>12</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G63" s="2" t="s">
         <v>105</v>
@@ -2857,13 +2848,13 @@
         <v>11</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="F64" s="3" t="s">
         <v>120</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>27</v>
+        <v>70</v>
       </c>
       <c r="H64" s="3" t="s">
         <v>20</v>
@@ -2960,32 +2951,32 @@
       </c>
     </row>
     <row r="68" spans="1:9">
-      <c r="A68" s="3">
+      <c r="A68" s="4">
         <v>67</v>
       </c>
-      <c r="B68" s="3" t="s">
+      <c r="B68" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="C68" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D68" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E68" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F68" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="G68" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="H68" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="I68" s="3" t="s">
-        <v>21</v>
+      <c r="C68" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D68" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E68" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F68" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G68" s="4">
+        <v>0</v>
+      </c>
+      <c r="H68" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I68" s="4" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="69" spans="1:9">
@@ -2993,25 +2984,25 @@
         <v>68</v>
       </c>
       <c r="B69" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F69" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="G69" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="H69" s="2" t="s">
         <v>131</v>
-      </c>
-      <c r="C69" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D69" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E69" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F69" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G69" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H69" s="2" t="s">
-        <v>134</v>
       </c>
       <c r="I69" s="2" t="s">
         <v>16</v>
@@ -3022,7 +3013,7 @@
         <v>69</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>10</v>
@@ -3034,13 +3025,13 @@
         <v>12</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="I70" s="2" t="s">
         <v>16</v>
@@ -3051,7 +3042,7 @@
         <v>70</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C71" s="4" t="s">
         <v>10</v>
@@ -3060,10 +3051,10 @@
         <v>11</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G71" s="4">
         <v>0</v>
@@ -3080,7 +3071,7 @@
         <v>71</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C72" s="4" t="s">
         <v>10</v>
@@ -3109,25 +3100,25 @@
         <v>72</v>
       </c>
       <c r="B73" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F73" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="G73" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="H73" s="2" t="s">
         <v>138</v>
-      </c>
-      <c r="C73" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D73" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E73" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F73" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="G73" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="H73" s="2" t="s">
-        <v>141</v>
       </c>
       <c r="I73" s="2" t="s">
         <v>16</v>
@@ -3138,7 +3129,7 @@
         <v>73</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C74" s="4" t="s">
         <v>10</v>
@@ -3167,7 +3158,7 @@
         <v>74</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C75" s="4" t="s">
         <v>10</v>
@@ -3196,7 +3187,7 @@
         <v>75</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C76" s="4" t="s">
         <v>10</v>
@@ -3225,7 +3216,7 @@
         <v>76</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C77" s="4" t="s">
         <v>10</v>
@@ -3254,115 +3245,115 @@
         <v>77</v>
       </c>
       <c r="B78" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="C78" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D78" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E78" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F78" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G78" s="4">
+        <v>0</v>
+      </c>
+      <c r="H78" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I78" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9">
+      <c r="A79" s="6">
+        <v>78</v>
+      </c>
+      <c r="B79" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="C79" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D79" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E79" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F79" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="G79" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H79" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="C78" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D78" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E78" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F78" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G78" s="4">
-        <v>0</v>
-      </c>
-      <c r="H78" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="I78" s="4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="79" spans="1:9">
-      <c r="A79" s="5">
-        <v>78</v>
-      </c>
-      <c r="B79" s="5" t="s">
+      <c r="I79" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9">
+      <c r="A80" s="6">
+        <v>79</v>
+      </c>
+      <c r="B80" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="C79" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D79" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E79" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F79" s="5" t="s">
+      <c r="C80" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D80" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E80" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F80" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="G79" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="H79" s="5" t="s">
+      <c r="G80" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="I79" s="5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="80" spans="1:9">
-      <c r="A80" s="5">
-        <v>79</v>
-      </c>
-      <c r="B80" s="5" t="s">
+      <c r="H80" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="C80" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D80" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E80" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F80" s="5" t="s">
+      <c r="I80" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9">
+      <c r="A81" s="6">
+        <v>80</v>
+      </c>
+      <c r="B81" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="G80" s="5" t="s">
+      <c r="C81" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D81" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E81" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="F81" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="H80" s="5" t="s">
+      <c r="G81" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="I80" s="5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="81" spans="1:9">
-      <c r="A81" s="5">
-        <v>80</v>
-      </c>
-      <c r="B81" s="5" t="s">
+      <c r="H81" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="C81" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D81" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E81" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="F81" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="G81" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="H81" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="I81" s="5" t="s">
-        <v>29</v>
+      <c r="I81" s="6" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="82" spans="1:9">
@@ -3370,7 +3361,7 @@
         <v>81</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>10</v>
@@ -3395,32 +3386,32 @@
       </c>
     </row>
     <row r="83" spans="1:9">
-      <c r="A83" s="6">
+      <c r="A83" s="5">
         <v>82</v>
       </c>
-      <c r="B83" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="C83" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D83" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E83" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F83" s="6" t="s">
+      <c r="B83" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="C83" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D83" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E83" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F83" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="G83" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="H83" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="I83" s="6" t="s">
-        <v>65</v>
+      <c r="G83" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="H83" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="I83" s="5" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="84" spans="1:9">
@@ -3428,7 +3419,7 @@
         <v>83</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C84" s="4" t="s">
         <v>10</v>
@@ -3457,7 +3448,7 @@
         <v>84</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C85" s="4" t="s">
         <v>10</v>
@@ -3486,7 +3477,7 @@
         <v>85</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C86" s="4" t="s">
         <v>10</v>
@@ -3515,57 +3506,57 @@
         <v>86</v>
       </c>
       <c r="B87" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="C87" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D87" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E87" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F87" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G87" s="4">
+        <v>0</v>
+      </c>
+      <c r="H87" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I87" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9">
+      <c r="A88" s="6">
+        <v>87</v>
+      </c>
+      <c r="B88" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="C88" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D88" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E88" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F88" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="G88" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="C87" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D87" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E87" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F87" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G87" s="4">
-        <v>0</v>
-      </c>
-      <c r="H87" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="I87" s="4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="88" spans="1:9">
-      <c r="A88" s="5">
-        <v>87</v>
-      </c>
-      <c r="B88" s="5" t="s">
+      <c r="H88" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="C88" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D88" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E88" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F88" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="G88" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="H88" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="I88" s="5" t="s">
-        <v>29</v>
+      <c r="I88" s="6" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="89" spans="1:9">
@@ -3573,25 +3564,25 @@
         <v>88</v>
       </c>
       <c r="B89" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F89" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="G89" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="H89" s="2" t="s">
         <v>169</v>
-      </c>
-      <c r="C89" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D89" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E89" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F89" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="G89" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="H89" s="2" t="s">
-        <v>172</v>
       </c>
       <c r="I89" s="2" t="s">
         <v>16</v>
@@ -3602,7 +3593,7 @@
         <v>89</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C90" s="4" t="s">
         <v>10</v>
@@ -3631,7 +3622,7 @@
         <v>90</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="C91" s="4" t="s">
         <v>10</v>
@@ -3660,7 +3651,7 @@
         <v>91</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C92" s="4" t="s">
         <v>10</v>
@@ -3689,7 +3680,7 @@
         <v>92</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C93" s="4" t="s">
         <v>10</v>
@@ -3718,7 +3709,7 @@
         <v>93</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="C94" s="4" t="s">
         <v>10</v>
@@ -3747,7 +3738,7 @@
         <v>94</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="C95" s="4" t="s">
         <v>10</v>
@@ -3776,7 +3767,7 @@
         <v>95</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="C96" s="4" t="s">
         <v>10</v>
@@ -3801,61 +3792,61 @@
       </c>
     </row>
     <row r="97" spans="1:9">
-      <c r="A97" s="5">
+      <c r="A97" s="6">
         <v>96</v>
       </c>
-      <c r="B97" s="5" t="s">
+      <c r="B97" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="C97" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D97" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E97" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F97" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="G97" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="H97" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="C97" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D97" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E97" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F97" s="5" t="s">
+      <c r="I97" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9">
+      <c r="A98" s="6">
+        <v>97</v>
+      </c>
+      <c r="B98" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="G97" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="H97" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="I97" s="5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="98" spans="1:9">
-      <c r="A98" s="5">
-        <v>97</v>
-      </c>
-      <c r="B98" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="C98" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D98" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E98" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F98" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="G98" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="H98" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="I98" s="5" t="s">
-        <v>29</v>
+      <c r="C98" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D98" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E98" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F98" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="G98" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="H98" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="I98" s="6" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="99" spans="1:9">
@@ -3863,25 +3854,25 @@
         <v>98</v>
       </c>
       <c r="B99" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E99" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F99" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="G99" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="H99" s="2" t="s">
         <v>185</v>
-      </c>
-      <c r="C99" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D99" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E99" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F99" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="G99" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="H99" s="2" t="s">
-        <v>188</v>
       </c>
       <c r="I99" s="2" t="s">
         <v>16</v>
@@ -3892,7 +3883,7 @@
         <v>99</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C100" s="4" t="s">
         <v>10</v>
